--- a/resources/table/enum.item.xlsx
+++ b/resources/table/enum.item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\CSHYEON\Data\git\game\c++\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD0FFDB-CB3B-4582-843D-F106117693F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA04EEC-63A5-4814-8AEE-0C5384A9AB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16E011AE-D02E-4FC8-8F56-7E58FFC8504B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{16E011AE-D02E-4FC8-8F56-7E58FFC8504B}"/>
   </bookViews>
   <sheets>
     <sheet name="ITEM_TYPE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,10 +86,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>BOW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NONE</t>
   </si>
   <si>
@@ -129,9 +125,6 @@
     <t>AUXILIARY</t>
   </si>
   <si>
-    <t>ARROW</t>
-  </si>
-  <si>
     <t>0x00000000</t>
   </si>
   <si>
@@ -169,9 +162,6 @@
   </si>
   <si>
     <t>EQUIPMENT | 0x00002000</t>
-  </si>
-  <si>
-    <t>EQUIPMENT | 0x00004000</t>
   </si>
   <si>
     <t>NORMAL</t>
@@ -680,94 +670,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFF18F3C-64BA-4578-B1EB-62F11CEBE98C}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B11">
+      <c r="B10" s="1">
         <v>11</v>
       </c>
     </row>
@@ -779,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FF91FD-C4B3-443D-A8F3-AB1BBBDCFB6C}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1" bestFit="1" customWidth="1"/>
@@ -789,114 +774,106 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +893,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1">
         <v>0</v>
@@ -924,7 +901,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -932,7 +909,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -940,7 +917,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -948,7 +925,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -1042,106 +1019,106 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1137,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1">
         <v>0</v>
@@ -1168,7 +1145,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1176,7 +1153,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1184,7 +1161,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -1192,7 +1169,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -1200,7 +1177,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1">
         <v>7</v>
@@ -1208,7 +1185,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1">
         <v>8</v>
@@ -1216,7 +1193,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1">
         <v>20</v>
@@ -1224,7 +1201,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1">
         <v>21</v>
@@ -1243,7 +1220,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B1">
         <v>0</v>
@@ -1251,7 +1228,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B2">
         <v>1</v>
